--- a/Data_Table/사람 테이블.xlsx
+++ b/Data_Table/사람 테이블.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Human" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Human_Line" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Situation_Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human_Line" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Situation_Type" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1385,6 +1385,114 @@
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>실험 장비가!</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>91035</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>90003</v>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>Raid</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>저기 있다!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>91036</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>90003</v>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>Raid</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>전원 포획!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>91037</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>90003</v>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>Raid</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>한 마리도 놓치지 마!</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>91038</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>90003</v>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>Raid_Catch</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>한 마리 잡았다!</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>91039</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>90003</v>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>Raid_Catch</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>가만히 있어!</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>91040</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>90003</v>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Raid_Catch</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>포획 완료!</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1502,6 +1610,30 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Raid</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>게임 오버 습격: 몰려오며 외칠 때 (경비원)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Raid_Catch</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>게임 오버 습격: 쥐를 잡았을 때 (경비원)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/사람 테이블.xlsx
+++ b/Data_Table/사람 테이블.xlsx
@@ -423,12 +423,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -449,30 +449,35 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>코드 id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>체력 배율</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>치즈 배율</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>속도 배율</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>첫 등장 층</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>에셋 폴더</t>
         </is>
@@ -491,30 +496,35 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>human_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>code_id</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>hp_mul</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>value_mul</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>speed_mul</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>from_floor</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>asset_folder</t>
         </is>
@@ -533,30 +543,35 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -571,24 +586,27 @@
           <t>연구원</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>3390001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>researcher</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="E4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="F4" s="1" t="n">
         <v>6</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>1</v>
       </c>
       <c r="G4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Humans/Parts/researcher</t>
         </is>
@@ -603,24 +621,27 @@
           <t>청소부</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>3390002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>janitor</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="E5" s="1" t="n">
         <v>3.5</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>0.9</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Humans/Parts/janitor</t>
         </is>
@@ -635,24 +656,27 @@
           <t>경비원</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>3390003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>guard</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>1.1</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Humans/Parts/guard</t>
         </is>
@@ -667,24 +691,27 @@
           <t>요리사</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>3390004</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>cook</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="E7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.95</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Humans/Parts/cook</t>
         </is>
@@ -701,13 +728,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -731,6 +759,11 @@
           <t>대사</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>대사 키</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -753,6 +786,11 @@
           <t>text</t>
         </is>
       </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>text_sk</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -773,6 +811,11 @@
       <c r="D3" s="1" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -793,6 +836,9 @@
           <t>쥐, 쥐다아아!!</t>
         </is>
       </c>
+      <c r="E4" s="2" t="n">
+        <v>3491001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -811,6 +857,9 @@
           <t>실험체가 탈출했어!</t>
         </is>
       </c>
+      <c r="E5" s="2" t="n">
+        <v>3491002</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -829,6 +878,9 @@
           <t>꺄아아악!</t>
         </is>
       </c>
+      <c r="E6" s="2" t="n">
+        <v>3491003</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -847,6 +899,9 @@
           <t>내 논문!!</t>
         </is>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>3491004</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -865,6 +920,9 @@
           <t>으악 쥐!!</t>
         </is>
       </c>
+      <c r="E8" s="2" t="n">
+        <v>3491005</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -883,6 +941,9 @@
           <t>대걸레 어디 갔지?!</t>
         </is>
       </c>
+      <c r="E9" s="2" t="n">
+        <v>3491006</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -901,6 +962,9 @@
           <t>퇴근할래…</t>
         </is>
       </c>
+      <c r="E10" s="2" t="n">
+        <v>3491007</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -919,6 +983,9 @@
           <t>거, 거기 서!</t>
         </is>
       </c>
+      <c r="E11" s="2" t="n">
+        <v>3491008</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -937,6 +1004,9 @@
           <t>지원 요청!!</t>
         </is>
       </c>
+      <c r="E12" s="2" t="n">
+        <v>3491009</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -955,6 +1025,9 @@
           <t>나 무서운 거 싫어!!</t>
         </is>
       </c>
+      <c r="E13" s="2" t="n">
+        <v>3491010</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -973,6 +1046,9 @@
           <t>내 주방에 쥐가?!</t>
         </is>
       </c>
+      <c r="E14" s="2" t="n">
+        <v>3491011</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -991,6 +1067,9 @@
           <t>위생 점검 망했다!</t>
         </is>
       </c>
+      <c r="E15" s="2" t="n">
+        <v>3491012</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1009,6 +1088,9 @@
           <t>으악 쥐다!!</t>
         </is>
       </c>
+      <c r="E16" s="2" t="n">
+        <v>3491013</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1027,6 +1109,9 @@
           <t>누가 내 머리 잡아당겨?!</t>
         </is>
       </c>
+      <c r="E17" s="2" t="n">
+        <v>3491014</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1045,6 +1130,9 @@
           <t>아얏!</t>
         </is>
       </c>
+      <c r="E18" s="2" t="n">
+        <v>3491015</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1063,6 +1151,9 @@
           <t>물었어!!</t>
         </is>
       </c>
+      <c r="E19" s="2" t="n">
+        <v>3491016</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1081,6 +1172,9 @@
           <t>저리 가!</t>
         </is>
       </c>
+      <c r="E20" s="2" t="n">
+        <v>3491017</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1099,6 +1193,9 @@
           <t>히익!</t>
         </is>
       </c>
+      <c r="E21" s="2" t="n">
+        <v>3491018</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1117,6 +1214,9 @@
           <t>으아아아악~!</t>
         </is>
       </c>
+      <c r="E22" s="2" t="n">
+        <v>3491019</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1135,6 +1235,9 @@
           <t>엄마아아~!</t>
         </is>
       </c>
+      <c r="E23" s="2" t="n">
+        <v>3491020</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1153,6 +1256,9 @@
           <t>산재 처리 부탁해요…</t>
         </is>
       </c>
+      <c r="E24" s="2" t="n">
+        <v>3491021</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1171,6 +1277,9 @@
           <t>퇴사하겠습니다아아!</t>
         </is>
       </c>
+      <c r="E25" s="2" t="n">
+        <v>3491022</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1189,6 +1298,9 @@
           <t>월급 루팡 실패~</t>
         </is>
       </c>
+      <c r="E26" s="2" t="n">
+        <v>3491023</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1207,6 +1319,9 @@
           <t>논문 마감이…!</t>
         </is>
       </c>
+      <c r="E27" s="2" t="n">
+        <v>3491024</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1225,6 +1340,9 @@
           <t>(비명)</t>
         </is>
       </c>
+      <c r="E28" s="2" t="n">
+        <v>3491025</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1243,6 +1361,9 @@
           <t>이건 계약서에 없었어!!</t>
         </is>
       </c>
+      <c r="E29" s="2" t="n">
+        <v>3491026</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1261,6 +1382,9 @@
           <t>펑!!</t>
         </is>
       </c>
+      <c r="E30" s="2" t="n">
+        <v>3491027</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1279,6 +1403,9 @@
           <t>뿅!</t>
         </is>
       </c>
+      <c r="E31" s="2" t="n">
+        <v>3491028</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1297,6 +1424,9 @@
           <t>퐁!</t>
         </is>
       </c>
+      <c r="E32" s="2" t="n">
+        <v>3491029</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1315,6 +1445,9 @@
           <t>(퇴근 완료)</t>
         </is>
       </c>
+      <c r="E33" s="2" t="n">
+        <v>3491030</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1333,6 +1466,9 @@
           <t>(조퇴)</t>
         </is>
       </c>
+      <c r="E34" s="2" t="n">
+        <v>3491031</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1351,6 +1487,9 @@
           <t>누가 던졌어!</t>
         </is>
       </c>
+      <c r="E35" s="2" t="n">
+        <v>3491032</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1369,6 +1508,9 @@
           <t>아야야!</t>
         </is>
       </c>
+      <c r="E36" s="2" t="n">
+        <v>3491033</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1387,6 +1529,9 @@
           <t>실험 장비가!</t>
         </is>
       </c>
+      <c r="E37" s="2" t="n">
+        <v>3491034</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1405,6 +1550,9 @@
           <t>저기 있다!!</t>
         </is>
       </c>
+      <c r="E38" s="2" t="n">
+        <v>3491035</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1423,6 +1571,9 @@
           <t>전원 포획!!</t>
         </is>
       </c>
+      <c r="E39" s="2" t="n">
+        <v>3491036</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1441,6 +1592,9 @@
           <t>한 마리도 놓치지 마!</t>
         </is>
       </c>
+      <c r="E40" s="2" t="n">
+        <v>3491037</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1459,6 +1613,9 @@
           <t>한 마리 잡았다!</t>
         </is>
       </c>
+      <c r="E41" s="2" t="n">
+        <v>3491038</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1477,6 +1634,9 @@
           <t>가만히 있어!</t>
         </is>
       </c>
+      <c r="E42" s="2" t="n">
+        <v>3491039</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1494,6 +1654,9 @@
         <is>
           <t>포획 완료!</t>
         </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>3491040</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/사람 테이블.xlsx
+++ b/Data_Table/사람 테이블.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -482,6 +482,11 @@
           <t>에셋 폴더</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>사라지는 층 (0 = 계속)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -529,6 +534,11 @@
           <t>asset_folder</t>
         </is>
       </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>to_floor</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -574,6 +584,11 @@
       <c r="I3" s="1" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -611,6 +626,9 @@
           <t>Humans/Parts/researcher</t>
         </is>
       </c>
+      <c r="J4" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -646,6 +664,9 @@
           <t>Humans/Parts/janitor</t>
         </is>
       </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -715,6 +736,921 @@
         <is>
           <t>Humans/Parts/cook</t>
         </is>
+      </c>
+      <c r="J7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>90011</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>털 범벅 집사 연구원</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>3390011</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>catres</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/catres</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>90012</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>수의사</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>3390012</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>vet</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/vet</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>90013</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>사료 배달원</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3390013</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>feeder</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/feeder</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>90014</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>알레르기 연구원</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>3390014</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>allergy</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/allergy</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>90015</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>고생물학자</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>3390015</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>paleo</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/paleo</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>90016</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>조련사</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3390016</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>trainer</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/trainer</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>90017</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>견학 어린이</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>3390017</v>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>kid</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/kid</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>90018</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>매직 워드 프로그래머</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>3390018</v>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>nedry</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/nedry</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>90019</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>현장소장</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>3390019</v>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>harold</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/harold</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>90020</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>신호수</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>3390020</v>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>flagger</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/flagger</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>90021</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>믹스커피 인부</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>3390021</v>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>coffeeman</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/coffeeman</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>90022</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>철근 작업자</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>3390022</v>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>rebar</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/rebar</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>90023</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>해양학자</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>3390023</v>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>oceanog</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/oceanog</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>90024</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>다이버</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>3390024</v>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>diver</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/diver</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>90025</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>생선 경매사</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>3390025</v>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>auctioneer</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/auctioneer</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>90026</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>소금 뿌리는 사장</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>3390026</v>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>saltbae</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/saltbae</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>90027</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>노병 해설사</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>3390027</v>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>veteran</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/veteran</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>90028</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>군복 재연 배우</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>3390028</v>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>reenactor</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/reenactor</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>90029</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>견학 학생</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>3390029</v>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>student</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/student</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>90030</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>통신병</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>3390030</v>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>radioman</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/radioman</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>90031</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>관제사</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>3390031</v>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>controller</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/controller</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>90032</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>바나나 우주비행사</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>3390032</v>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>astro_banana</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/astro_banana</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>90033</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>조명 우주비행사</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>3390033</v>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>astro_set</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/astro_set</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>90034</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>커피 쏟는 관제소장</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>3390034</v>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>flightdir</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>91</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Humans/Parts/flightdir</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -728,7 +1664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1657,6 +2593,1014 @@
       </c>
       <c r="E43" s="2" t="n">
         <v>3491040</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>91101</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>90011</v>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>내 실험복이 털 범벅이야!</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>3491101</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>91102</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>90011</v>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>냥이들 밥 줄 시간인데!</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>3491102</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>91103</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>90012</v>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>쥐는 진료 안 해요!!</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>3491103</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>91104</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>90012</v>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>주사 맞을래?!</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>3491104</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>91105</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>90013</v>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>배송 지연이에요!</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>3491105</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>91106</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>90013</v>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>사료 봉지 물지 마!</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>3491106</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>91107</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>90014</v>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>에, 에취!!</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>3491107</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>91108</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>90014</v>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>쥐 알레르기도 있었나?!</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>3491108</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>91109</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>90015</v>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>화석 건드리지 마!</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>3491109</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>91110</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>90015</v>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>이건 백악기 유물이라고!</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>3491110</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>91111</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>90016</v>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>진정해, 진정!</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>3491111</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>91112</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>90016</v>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>랩터보다 빠르잖아!</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>3491112</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>91113</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>90017</v>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>엄마, 쥐가 막 뛰어!</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>3491113</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>91114</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>90017</v>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>와 쥐다! 귀여워!</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>3491114</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>91115</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>90018</v>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>아아아, 매직 워드를 말 안 했잖아!</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>3491115</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>91116</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>90018</v>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>시스템 다운이다!</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>3491116</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>91117</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>90019</v>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>하하… 괜찮아요… (안 괜찮음)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>3491117</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>91118</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>90019</v>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>무재해 기록이 깨진다!</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>3491118</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>91119</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>90020</v>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>멈춰! 멈추라고!</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>3491119</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>91120</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>90020</v>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>차량 통제 중!</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>3491120</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>91121</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>90021</v>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>커피 타는 중이었는데!</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>3491121</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>91122</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>90021</v>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>봉지로 젓는 게 국룰인데!</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>3491122</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>91123</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>90022</v>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>철근 무너진다!</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>3491123</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>91124</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>90022</v>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>안전모 써!</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>3491124</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>91125</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>90023</v>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>샘플이 도망간다!</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>3491125</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>91126</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>90023</v>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>쥐는 해양 생물이 아냐!</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>3491126</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>91127</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>90024</v>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>꼬르륵… 쥐다!</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>3491127</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>91128</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>90024</v>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>산소통 물지 마!</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>3491128</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>91129</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>90025</v>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>묻고 더블로 가!</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>3491129</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>91130</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>90025</v>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>이 쥐 싯가요!</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>3491130</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>91131</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>90026</v>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>소금 맛 좀 볼래?!</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>3491131</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>91132</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>90026</v>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>내 팔꿈치 각도가!</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>3491132</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>91133</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>90027</v>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>내가 왕년에 말이야!</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>3491133</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>91134</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>90027</v>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>전시물 만지지 마!</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>3491134</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>91135</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>90028</v>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>이건 대본에 없었어!</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>3491135</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>91136</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>90028</v>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>엄폐! 엄폐!</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>3491136</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>91137</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>90029</v>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>숙제 사진 찍어야 돼!</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>3491137</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>91138</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>90029</v>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>선생님, 쥐요!!</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>3491138</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>91139</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>90030</v>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>여기는 박물관, 쥐 출현!</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>3491139</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>91140</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>90030</v>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>치직… 응답하라!</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>3491140</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>91141</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>90031</v>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>휴스턴, 문제가 생겼다!</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>3491141</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>91142</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>90031</v>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>궤도 이탈!</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>3491142</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>91143</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>90032</v>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>원래 이랬어. (Always has been)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>3491143</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>91144</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>90032</v>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>바나나 내려놔!</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>3491144</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>91145</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>90033</v>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>컷! 컷! 다시 찍어!</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>3491145</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>91146</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>90033</v>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>조명 넘어진다!</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>3491146</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>91147</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>90034</v>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>내 커피!!</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>3491147</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>91148</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>90034</v>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>Panic</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>발사 중지!</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>3491148</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/사람 테이블.xlsx
+++ b/Data_Table/사람 테이블.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Human" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Human_Line" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Situation_Type" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human_Line" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Situation_Type" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
